--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T09:01:58+00:00</t>
+    <t>2025-07-01T09:24:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T09:24:19+00:00</t>
+    <t>2025-07-01T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T10:10:16+00:00</t>
+    <t>2025-07-01T10:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -132,7 +132,7 @@
     <t>Context</t>
   </si>
   <si>
-    <t>element:Element</t>
+    <t>element:Extension</t>
   </si>
   <si>
     <t>ID</t>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="124">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T10:32:14+00:00</t>
+    <t>2025-07-01T10:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -346,6 +346,9 @@
   <si>
     <t xml:space="preserve">Extension {http://jpfhir.jp/fhir/core/StructureDefinition/JP_Observation_DentalOral_BodyStructure_BodyLandmarkOrientation}
 </t>
+  </si>
+  <si>
+    <t>JP Observation DentalOral BodyStructure BodyLandmarkOrientation</t>
   </si>
   <si>
     <t>Extension.extension:qualifier</t>
@@ -1412,7 +1415,7 @@
         <v>107</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="M7" t="s" s="2">
         <v>92</v>
@@ -1486,13 +1489,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>77</v>
@@ -1514,10 +1517,10 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="M8" t="s" s="2">
         <v>92</v>
@@ -1591,10 +1594,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1617,16 +1620,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1676,7 +1679,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>84</v>
@@ -1691,15 +1694,15 @@
         <v>77</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1722,13 +1725,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1779,7 +1782,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1791,10 +1794,10 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T10:47:42+00:00</t>
+    <t>2025-07-01T10:50:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="128">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T10:50:12+00:00</t>
+    <t>2025-07-01T11:07:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>特定の歯を格納するための拡張</t>
+    <t>内部に含まれる構造の拡張</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -325,6 +325,9 @@
     <t>JP Observation DentalOral BodyStructure Structure</t>
   </si>
   <si>
+    <t>構造に関する拡張</t>
+  </si>
+  <si>
     <t>Extension.extension:laterality</t>
   </si>
   <si>
@@ -338,6 +341,9 @@
     <t>JP Observation DentalOral BodyStructure Laterality</t>
   </si>
   <si>
+    <t>左右をあらわす拡張</t>
+  </si>
+  <si>
     <t>Extension.extension:bodyLandmarkOrientation</t>
   </si>
   <si>
@@ -351,6 +357,9 @@
     <t>JP Observation DentalOral BodyStructure BodyLandmarkOrientation</t>
   </si>
   <si>
+    <t>ランドマークに関する拡張</t>
+  </si>
+  <si>
     <t>Extension.extension:qualifier</t>
   </si>
   <si>
@@ -362,6 +371,9 @@
   </si>
   <si>
     <t>JP Observation DentalOral BodyStructure Qualifier</t>
+  </si>
+  <si>
+    <t>修飾子に関する拡張</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -1208,7 +1220,7 @@
         <v>100</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1279,13 +1291,13 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B6" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C6" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s" s="2">
         <v>77</v>
@@ -1307,13 +1319,13 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1384,13 +1396,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B7" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C7" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D7" t="s" s="2">
         <v>77</v>
@@ -1412,13 +1424,13 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1489,13 +1501,13 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B8" t="s" s="2">
         <v>90</v>
       </c>
       <c r="C8" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s" s="2">
         <v>77</v>
@@ -1517,13 +1529,13 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>92</v>
+        <v>116</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1594,10 +1606,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1620,16 +1632,16 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1679,7 +1691,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>84</v>
@@ -1694,15 +1706,15 @@
         <v>77</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1725,13 +1737,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1782,7 +1794,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1794,10 +1806,10 @@
         <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T11:07:42+00:00</t>
+    <t>2025-07-01T11:59:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
+++ b/jpcore-r4/feature/mod_dental_bodyStructureExtensions/StructureDefinition-jp-observation-dentaloral-bodystructure-includedstructure.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-01T11:59:02+00:00</t>
+    <t>2025-07-01T12:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
